--- a/Result/CoberturaFinal.xlsx
+++ b/Result/CoberturaFinal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G337"/>
+  <dimension ref="A1:H337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Cubierto</t>
+          <t>Ideal_Cubierto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Real_Cubierto</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Under</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Over</t>
         </is>
@@ -493,6 +498,9 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +530,9 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +562,9 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +594,9 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +626,9 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +658,9 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +690,9 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +722,9 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +754,9 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +786,9 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +818,9 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +850,9 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +882,9 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +914,9 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -894,9 +941,12 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>12</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -923,9 +973,12 @@
         <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -952,9 +1005,12 @@
         <v>192</v>
       </c>
       <c r="F18" t="n">
+        <v>192</v>
+      </c>
+      <c r="G18" t="n">
         <v>188</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -981,9 +1037,12 @@
         <v>318</v>
       </c>
       <c r="F19" t="n">
+        <v>318</v>
+      </c>
+      <c r="G19" t="n">
         <v>82</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,9 +1069,12 @@
         <v>348</v>
       </c>
       <c r="F20" t="n">
+        <v>348</v>
+      </c>
+      <c r="G20" t="n">
         <v>68</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1039,9 +1101,12 @@
         <v>418</v>
       </c>
       <c r="F21" t="n">
+        <v>418</v>
+      </c>
+      <c r="G21" t="n">
         <v>22</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1068,9 +1133,12 @@
         <v>418</v>
       </c>
       <c r="F22" t="n">
+        <v>418</v>
+      </c>
+      <c r="G22" t="n">
         <v>45</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1097,9 +1165,12 @@
         <v>418</v>
       </c>
       <c r="F23" t="n">
+        <v>418</v>
+      </c>
+      <c r="G23" t="n">
         <v>45</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1126,9 +1197,12 @@
         <v>418</v>
       </c>
       <c r="F24" t="n">
+        <v>418</v>
+      </c>
+      <c r="G24" t="n">
         <v>47</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1155,9 +1229,12 @@
         <v>418</v>
       </c>
       <c r="F25" t="n">
+        <v>418</v>
+      </c>
+      <c r="G25" t="n">
         <v>83</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1184,9 +1261,12 @@
         <v>403</v>
       </c>
       <c r="F26" t="n">
+        <v>403</v>
+      </c>
+      <c r="G26" t="n">
         <v>98</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1213,9 +1293,12 @@
         <v>418</v>
       </c>
       <c r="F27" t="n">
+        <v>418</v>
+      </c>
+      <c r="G27" t="n">
         <v>83</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1242,9 +1325,12 @@
         <v>418</v>
       </c>
       <c r="F28" t="n">
+        <v>418</v>
+      </c>
+      <c r="G28" t="n">
         <v>84</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1271,9 +1357,12 @@
         <v>418</v>
       </c>
       <c r="F29" t="n">
+        <v>418</v>
+      </c>
+      <c r="G29" t="n">
         <v>84</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1300,9 +1389,12 @@
         <v>418</v>
       </c>
       <c r="F30" t="n">
+        <v>418</v>
+      </c>
+      <c r="G30" t="n">
         <v>82</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1329,9 +1421,12 @@
         <v>418</v>
       </c>
       <c r="F31" t="n">
+        <v>418</v>
+      </c>
+      <c r="G31" t="n">
         <v>82</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1358,9 +1453,12 @@
         <v>418</v>
       </c>
       <c r="F32" t="n">
+        <v>418</v>
+      </c>
+      <c r="G32" t="n">
         <v>79</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1387,9 +1485,12 @@
         <v>418</v>
       </c>
       <c r="F33" t="n">
+        <v>418</v>
+      </c>
+      <c r="G33" t="n">
         <v>79</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1416,9 +1517,12 @@
         <v>418</v>
       </c>
       <c r="F34" t="n">
+        <v>418</v>
+      </c>
+      <c r="G34" t="n">
         <v>70</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1445,9 +1549,12 @@
         <v>418</v>
       </c>
       <c r="F35" t="n">
+        <v>418</v>
+      </c>
+      <c r="G35" t="n">
         <v>54</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1474,9 +1581,12 @@
         <v>301</v>
       </c>
       <c r="F36" t="n">
+        <v>301</v>
+      </c>
+      <c r="G36" t="n">
         <v>148</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,9 +1613,12 @@
         <v>121</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1532,9 +1645,12 @@
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1561,9 +1677,12 @@
         <v>70</v>
       </c>
       <c r="F39" t="n">
+        <v>70</v>
+      </c>
+      <c r="G39" t="n">
         <v>15</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,9 +1709,12 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>60</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1619,9 +1741,12 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
         <v>37</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1648,9 +1773,12 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>37</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1677,9 +1805,12 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>37</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1711,6 +1842,9 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1874,9 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1906,9 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +1938,9 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +1970,9 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2002,9 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2034,9 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2066,9 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2098,9 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2130,9 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2162,9 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2194,9 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2226,9 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2258,9 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2290,9 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2322,9 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2354,9 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2386,9 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2418,9 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2450,9 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2286,9 +2477,12 @@
         <v>2</v>
       </c>
       <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
         <v>9</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2315,9 +2509,12 @@
         <v>17</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2344,9 +2541,12 @@
         <v>203</v>
       </c>
       <c r="F66" t="n">
+        <v>203</v>
+      </c>
+      <c r="G66" t="n">
         <v>157</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2373,9 +2573,12 @@
         <v>338</v>
       </c>
       <c r="F67" t="n">
+        <v>338</v>
+      </c>
+      <c r="G67" t="n">
         <v>36</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2402,9 +2605,12 @@
         <v>418</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2431,9 +2637,12 @@
         <v>418</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2460,9 +2669,12 @@
         <v>418</v>
       </c>
       <c r="F70" t="n">
+        <v>418</v>
+      </c>
+      <c r="G70" t="n">
         <v>4</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2489,9 +2701,12 @@
         <v>418</v>
       </c>
       <c r="F71" t="n">
+        <v>418</v>
+      </c>
+      <c r="G71" t="n">
         <v>5</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2518,9 +2733,12 @@
         <v>418</v>
       </c>
       <c r="F72" t="n">
+        <v>418</v>
+      </c>
+      <c r="G72" t="n">
         <v>9</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2547,9 +2765,12 @@
         <v>418</v>
       </c>
       <c r="F73" t="n">
+        <v>418</v>
+      </c>
+      <c r="G73" t="n">
         <v>39</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2576,9 +2797,12 @@
         <v>403</v>
       </c>
       <c r="F74" t="n">
+        <v>403</v>
+      </c>
+      <c r="G74" t="n">
         <v>54</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2605,9 +2829,12 @@
         <v>418</v>
       </c>
       <c r="F75" t="n">
+        <v>418</v>
+      </c>
+      <c r="G75" t="n">
         <v>39</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2634,9 +2861,12 @@
         <v>418</v>
       </c>
       <c r="F76" t="n">
+        <v>418</v>
+      </c>
+      <c r="G76" t="n">
         <v>40</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2663,9 +2893,12 @@
         <v>418</v>
       </c>
       <c r="F77" t="n">
+        <v>418</v>
+      </c>
+      <c r="G77" t="n">
         <v>40</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2692,9 +2925,12 @@
         <v>418</v>
       </c>
       <c r="F78" t="n">
+        <v>418</v>
+      </c>
+      <c r="G78" t="n">
         <v>37</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2721,9 +2957,12 @@
         <v>418</v>
       </c>
       <c r="F79" t="n">
+        <v>418</v>
+      </c>
+      <c r="G79" t="n">
         <v>37</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2750,9 +2989,12 @@
         <v>418</v>
       </c>
       <c r="F80" t="n">
+        <v>418</v>
+      </c>
+      <c r="G80" t="n">
         <v>35</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2779,9 +3021,12 @@
         <v>418</v>
       </c>
       <c r="F81" t="n">
+        <v>418</v>
+      </c>
+      <c r="G81" t="n">
         <v>35</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2808,9 +3053,12 @@
         <v>418</v>
       </c>
       <c r="F82" t="n">
+        <v>418</v>
+      </c>
+      <c r="G82" t="n">
         <v>24</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2837,9 +3085,12 @@
         <v>416</v>
       </c>
       <c r="F83" t="n">
+        <v>416</v>
+      </c>
+      <c r="G83" t="n">
         <v>11</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2866,9 +3117,12 @@
         <v>290</v>
       </c>
       <c r="F84" t="n">
+        <v>290</v>
+      </c>
+      <c r="G84" t="n">
         <v>112</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2895,9 +3149,12 @@
         <v>95</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2924,9 +3181,12 @@
         <v>80</v>
       </c>
       <c r="F86" t="n">
+        <v>80</v>
+      </c>
+      <c r="G86" t="n">
         <v>1</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2953,9 +3213,12 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
         <v>69</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2982,9 +3245,12 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
         <v>48</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3011,9 +3277,12 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
         <v>34</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3040,9 +3309,12 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
         <v>34</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3069,9 +3341,12 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>32</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3103,6 +3378,9 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3132,6 +3410,9 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3161,6 +3442,9 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3190,6 +3474,9 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3219,6 +3506,9 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3248,6 +3538,9 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3277,6 +3570,9 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3306,6 +3602,9 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3335,6 +3634,9 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3364,6 +3666,9 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3393,6 +3698,9 @@
       <c r="G102" t="n">
         <v>0</v>
       </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3422,6 +3730,9 @@
       <c r="G103" t="n">
         <v>0</v>
       </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3451,6 +3762,9 @@
       <c r="G104" t="n">
         <v>0</v>
       </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3480,6 +3794,9 @@
       <c r="G105" t="n">
         <v>0</v>
       </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3509,6 +3826,9 @@
       <c r="G106" t="n">
         <v>0</v>
       </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3538,6 +3858,9 @@
       <c r="G107" t="n">
         <v>0</v>
       </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3567,6 +3890,9 @@
       <c r="G108" t="n">
         <v>0</v>
       </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3596,6 +3922,9 @@
       <c r="G109" t="n">
         <v>0</v>
       </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3625,6 +3954,9 @@
       <c r="G110" t="n">
         <v>0</v>
       </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3654,6 +3986,9 @@
       <c r="G111" t="n">
         <v>0</v>
       </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3678,9 +4013,12 @@
         <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3707,9 +4045,12 @@
         <v>17</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3736,9 +4077,12 @@
         <v>213</v>
       </c>
       <c r="F114" t="n">
+        <v>213</v>
+      </c>
+      <c r="G114" t="n">
         <v>106</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3765,9 +4109,12 @@
         <v>331</v>
       </c>
       <c r="F115" t="n">
+        <v>331</v>
+      </c>
+      <c r="G115" t="n">
         <v>5</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3794,9 +4141,12 @@
         <v>411</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
         <v>64</v>
       </c>
     </row>
@@ -3823,9 +4173,12 @@
         <v>411</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
         <v>47</v>
       </c>
     </row>
@@ -3852,9 +4205,12 @@
         <v>400</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3881,9 +4237,12 @@
         <v>385</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3910,9 +4269,12 @@
         <v>389</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3939,9 +4301,12 @@
         <v>404</v>
       </c>
       <c r="F121" t="n">
+        <v>404</v>
+      </c>
+      <c r="G121" t="n">
         <v>9</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3968,9 +4333,12 @@
         <v>396</v>
       </c>
       <c r="F122" t="n">
+        <v>396</v>
+      </c>
+      <c r="G122" t="n">
         <v>15</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3997,9 +4365,12 @@
         <v>411</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4026,9 +4397,12 @@
         <v>411</v>
       </c>
       <c r="F124" t="n">
+        <v>411</v>
+      </c>
+      <c r="G124" t="n">
         <v>2</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4055,9 +4429,12 @@
         <v>411</v>
       </c>
       <c r="F125" t="n">
+        <v>411</v>
+      </c>
+      <c r="G125" t="n">
         <v>2</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4084,9 +4461,12 @@
         <v>411</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4113,9 +4493,12 @@
         <v>411</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4142,9 +4525,12 @@
         <v>409</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4171,9 +4557,12 @@
         <v>402</v>
       </c>
       <c r="F129" t="n">
+        <v>402</v>
+      </c>
+      <c r="G129" t="n">
         <v>7</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4200,9 +4589,12 @@
         <v>398</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4229,9 +4621,12 @@
         <v>381</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4258,9 +4653,12 @@
         <v>280</v>
       </c>
       <c r="F132" t="n">
+        <v>280</v>
+      </c>
+      <c r="G132" t="n">
         <v>79</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4287,9 +4685,12 @@
         <v>95</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4316,9 +4717,12 @@
         <v>76</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4345,9 +4749,12 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
         <v>66</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4374,9 +4781,12 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
         <v>48</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4403,9 +4813,12 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
         <v>30</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4432,9 +4845,12 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
         <v>29</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4461,9 +4877,12 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
         <v>27</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4495,6 +4914,9 @@
       <c r="G140" t="n">
         <v>0</v>
       </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4524,6 +4946,9 @@
       <c r="G141" t="n">
         <v>0</v>
       </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4553,6 +4978,9 @@
       <c r="G142" t="n">
         <v>0</v>
       </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4582,6 +5010,9 @@
       <c r="G143" t="n">
         <v>0</v>
       </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4611,6 +5042,9 @@
       <c r="G144" t="n">
         <v>0</v>
       </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4640,6 +5074,9 @@
       <c r="G145" t="n">
         <v>0</v>
       </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4669,6 +5106,9 @@
       <c r="G146" t="n">
         <v>0</v>
       </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4698,6 +5138,9 @@
       <c r="G147" t="n">
         <v>0</v>
       </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4727,6 +5170,9 @@
       <c r="G148" t="n">
         <v>0</v>
       </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4756,6 +5202,9 @@
       <c r="G149" t="n">
         <v>0</v>
       </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4785,6 +5234,9 @@
       <c r="G150" t="n">
         <v>0</v>
       </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4814,6 +5266,9 @@
       <c r="G151" t="n">
         <v>0</v>
       </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4843,6 +5298,9 @@
       <c r="G152" t="n">
         <v>0</v>
       </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4872,6 +5330,9 @@
       <c r="G153" t="n">
         <v>0</v>
       </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4901,6 +5362,9 @@
       <c r="G154" t="n">
         <v>0</v>
       </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4930,6 +5394,9 @@
       <c r="G155" t="n">
         <v>0</v>
       </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4959,6 +5426,9 @@
       <c r="G156" t="n">
         <v>0</v>
       </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4988,6 +5458,9 @@
       <c r="G157" t="n">
         <v>0</v>
       </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5012,9 +5485,12 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>1</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5041,9 +5517,12 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
         <v>1</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5070,9 +5549,12 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
         <v>7</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5099,9 +5581,12 @@
         <v>10</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5128,9 +5613,12 @@
         <v>207</v>
       </c>
       <c r="F162" t="n">
+        <v>207</v>
+      </c>
+      <c r="G162" t="n">
         <v>155</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5157,9 +5645,12 @@
         <v>344</v>
       </c>
       <c r="F163" t="n">
+        <v>344</v>
+      </c>
+      <c r="G163" t="n">
         <v>32</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5186,9 +5677,12 @@
         <v>418</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
         <v>27</v>
       </c>
     </row>
@@ -5215,9 +5709,12 @@
         <v>418</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5244,9 +5741,12 @@
         <v>418</v>
       </c>
       <c r="F166" t="n">
+        <v>418</v>
+      </c>
+      <c r="G166" t="n">
         <v>10</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5273,9 +5773,12 @@
         <v>418</v>
       </c>
       <c r="F167" t="n">
+        <v>418</v>
+      </c>
+      <c r="G167" t="n">
         <v>10</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5302,9 +5805,12 @@
         <v>418</v>
       </c>
       <c r="F168" t="n">
+        <v>418</v>
+      </c>
+      <c r="G168" t="n">
         <v>11</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5331,9 +5837,12 @@
         <v>418</v>
       </c>
       <c r="F169" t="n">
+        <v>418</v>
+      </c>
+      <c r="G169" t="n">
         <v>35</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5360,9 +5869,12 @@
         <v>403</v>
       </c>
       <c r="F170" t="n">
+        <v>403</v>
+      </c>
+      <c r="G170" t="n">
         <v>51</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5389,9 +5901,12 @@
         <v>418</v>
       </c>
       <c r="F171" t="n">
+        <v>418</v>
+      </c>
+      <c r="G171" t="n">
         <v>36</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5418,9 +5933,12 @@
         <v>418</v>
       </c>
       <c r="F172" t="n">
+        <v>418</v>
+      </c>
+      <c r="G172" t="n">
         <v>36</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5447,9 +5965,12 @@
         <v>418</v>
       </c>
       <c r="F173" t="n">
+        <v>418</v>
+      </c>
+      <c r="G173" t="n">
         <v>36</v>
       </c>
-      <c r="G173" t="n">
+      <c r="H173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5476,9 +5997,12 @@
         <v>418</v>
       </c>
       <c r="F174" t="n">
+        <v>418</v>
+      </c>
+      <c r="G174" t="n">
         <v>33</v>
       </c>
-      <c r="G174" t="n">
+      <c r="H174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5505,9 +6029,12 @@
         <v>418</v>
       </c>
       <c r="F175" t="n">
+        <v>418</v>
+      </c>
+      <c r="G175" t="n">
         <v>33</v>
       </c>
-      <c r="G175" t="n">
+      <c r="H175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5534,9 +6061,12 @@
         <v>418</v>
       </c>
       <c r="F176" t="n">
+        <v>418</v>
+      </c>
+      <c r="G176" t="n">
         <v>31</v>
       </c>
-      <c r="G176" t="n">
+      <c r="H176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5563,9 +6093,12 @@
         <v>418</v>
       </c>
       <c r="F177" t="n">
+        <v>418</v>
+      </c>
+      <c r="G177" t="n">
         <v>31</v>
       </c>
-      <c r="G177" t="n">
+      <c r="H177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5592,9 +6125,12 @@
         <v>418</v>
       </c>
       <c r="F178" t="n">
+        <v>418</v>
+      </c>
+      <c r="G178" t="n">
         <v>24</v>
       </c>
-      <c r="G178" t="n">
+      <c r="H178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5621,9 +6157,12 @@
         <v>418</v>
       </c>
       <c r="F179" t="n">
+        <v>418</v>
+      </c>
+      <c r="G179" t="n">
         <v>12</v>
       </c>
-      <c r="G179" t="n">
+      <c r="H179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5650,9 +6189,12 @@
         <v>286</v>
       </c>
       <c r="F180" t="n">
+        <v>286</v>
+      </c>
+      <c r="G180" t="n">
         <v>104</v>
       </c>
-      <c r="G180" t="n">
+      <c r="H180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5679,9 +6221,12 @@
         <v>91</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5708,9 +6253,12 @@
         <v>74</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5737,9 +6285,12 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
         <v>62</v>
       </c>
-      <c r="G183" t="n">
+      <c r="H183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5766,9 +6317,12 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
         <v>45</v>
       </c>
-      <c r="G184" t="n">
+      <c r="H184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5795,9 +6349,12 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
         <v>27</v>
       </c>
-      <c r="G185" t="n">
+      <c r="H185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5824,9 +6381,12 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
         <v>27</v>
       </c>
-      <c r="G186" t="n">
+      <c r="H186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5853,9 +6413,12 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
         <v>26</v>
       </c>
-      <c r="G187" t="n">
+      <c r="H187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5887,6 +6450,9 @@
       <c r="G188" t="n">
         <v>0</v>
       </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5916,6 +6482,9 @@
       <c r="G189" t="n">
         <v>0</v>
       </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5945,6 +6514,9 @@
       <c r="G190" t="n">
         <v>0</v>
       </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5974,6 +6546,9 @@
       <c r="G191" t="n">
         <v>0</v>
       </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6003,6 +6578,9 @@
       <c r="G192" t="n">
         <v>0</v>
       </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6032,6 +6610,9 @@
       <c r="G193" t="n">
         <v>0</v>
       </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6061,6 +6642,9 @@
       <c r="G194" t="n">
         <v>0</v>
       </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6090,6 +6674,9 @@
       <c r="G195" t="n">
         <v>0</v>
       </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6119,6 +6706,9 @@
       <c r="G196" t="n">
         <v>0</v>
       </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6148,6 +6738,9 @@
       <c r="G197" t="n">
         <v>0</v>
       </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6177,6 +6770,9 @@
       <c r="G198" t="n">
         <v>0</v>
       </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6206,6 +6802,9 @@
       <c r="G199" t="n">
         <v>0</v>
       </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6235,6 +6834,9 @@
       <c r="G200" t="n">
         <v>0</v>
       </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6264,6 +6866,9 @@
       <c r="G201" t="n">
         <v>0</v>
       </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6293,6 +6898,9 @@
       <c r="G202" t="n">
         <v>0</v>
       </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6322,6 +6930,9 @@
       <c r="G203" t="n">
         <v>0</v>
       </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6351,6 +6962,9 @@
       <c r="G204" t="n">
         <v>0</v>
       </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6380,6 +6994,9 @@
       <c r="G205" t="n">
         <v>0</v>
       </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6409,6 +7026,9 @@
       <c r="G206" t="n">
         <v>0</v>
       </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6438,6 +7058,9 @@
       <c r="G207" t="n">
         <v>0</v>
       </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6462,9 +7085,12 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
         <v>6</v>
       </c>
-      <c r="G208" t="n">
+      <c r="H208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6491,9 +7117,12 @@
         <v>12</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6520,9 +7149,12 @@
         <v>268</v>
       </c>
       <c r="F210" t="n">
+        <v>268</v>
+      </c>
+      <c r="G210" t="n">
         <v>99</v>
       </c>
-      <c r="G210" t="n">
+      <c r="H210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6549,9 +7181,12 @@
         <v>331</v>
       </c>
       <c r="F211" t="n">
+        <v>331</v>
+      </c>
+      <c r="G211" t="n">
         <v>54</v>
       </c>
-      <c r="G211" t="n">
+      <c r="H211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6578,9 +7213,12 @@
         <v>418</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6607,9 +7245,12 @@
         <v>418</v>
       </c>
       <c r="F213" t="n">
+        <v>418</v>
+      </c>
+      <c r="G213" t="n">
         <v>4</v>
       </c>
-      <c r="G213" t="n">
+      <c r="H213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6636,9 +7277,12 @@
         <v>418</v>
       </c>
       <c r="F214" t="n">
+        <v>418</v>
+      </c>
+      <c r="G214" t="n">
         <v>20</v>
       </c>
-      <c r="G214" t="n">
+      <c r="H214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6665,9 +7309,12 @@
         <v>418</v>
       </c>
       <c r="F215" t="n">
+        <v>418</v>
+      </c>
+      <c r="G215" t="n">
         <v>20</v>
       </c>
-      <c r="G215" t="n">
+      <c r="H215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6694,9 +7341,12 @@
         <v>418</v>
       </c>
       <c r="F216" t="n">
+        <v>418</v>
+      </c>
+      <c r="G216" t="n">
         <v>22</v>
       </c>
-      <c r="G216" t="n">
+      <c r="H216" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6723,9 +7373,12 @@
         <v>418</v>
       </c>
       <c r="F217" t="n">
+        <v>418</v>
+      </c>
+      <c r="G217" t="n">
         <v>54</v>
       </c>
-      <c r="G217" t="n">
+      <c r="H217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6752,9 +7405,12 @@
         <v>412</v>
       </c>
       <c r="F218" t="n">
+        <v>412</v>
+      </c>
+      <c r="G218" t="n">
         <v>60</v>
       </c>
-      <c r="G218" t="n">
+      <c r="H218" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6781,9 +7437,12 @@
         <v>418</v>
       </c>
       <c r="F219" t="n">
+        <v>418</v>
+      </c>
+      <c r="G219" t="n">
         <v>54</v>
       </c>
-      <c r="G219" t="n">
+      <c r="H219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6810,9 +7469,12 @@
         <v>418</v>
       </c>
       <c r="F220" t="n">
+        <v>418</v>
+      </c>
+      <c r="G220" t="n">
         <v>55</v>
       </c>
-      <c r="G220" t="n">
+      <c r="H220" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6839,9 +7501,12 @@
         <v>418</v>
       </c>
       <c r="F221" t="n">
+        <v>418</v>
+      </c>
+      <c r="G221" t="n">
         <v>55</v>
       </c>
-      <c r="G221" t="n">
+      <c r="H221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6868,9 +7533,12 @@
         <v>418</v>
       </c>
       <c r="F222" t="n">
+        <v>418</v>
+      </c>
+      <c r="G222" t="n">
         <v>54</v>
       </c>
-      <c r="G222" t="n">
+      <c r="H222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6897,9 +7565,12 @@
         <v>418</v>
       </c>
       <c r="F223" t="n">
+        <v>418</v>
+      </c>
+      <c r="G223" t="n">
         <v>53</v>
       </c>
-      <c r="G223" t="n">
+      <c r="H223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6926,9 +7597,12 @@
         <v>418</v>
       </c>
       <c r="F224" t="n">
+        <v>418</v>
+      </c>
+      <c r="G224" t="n">
         <v>50</v>
       </c>
-      <c r="G224" t="n">
+      <c r="H224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6955,9 +7629,12 @@
         <v>418</v>
       </c>
       <c r="F225" t="n">
+        <v>418</v>
+      </c>
+      <c r="G225" t="n">
         <v>44</v>
       </c>
-      <c r="G225" t="n">
+      <c r="H225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6984,9 +7661,12 @@
         <v>418</v>
       </c>
       <c r="F226" t="n">
+        <v>418</v>
+      </c>
+      <c r="G226" t="n">
         <v>20</v>
       </c>
-      <c r="G226" t="n">
+      <c r="H226" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7013,9 +7693,12 @@
         <v>418</v>
       </c>
       <c r="F227" t="n">
+        <v>418</v>
+      </c>
+      <c r="G227" t="n">
         <v>13</v>
       </c>
-      <c r="G227" t="n">
+      <c r="H227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7042,9 +7725,12 @@
         <v>216</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7071,9 +7757,12 @@
         <v>105</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7100,9 +7789,12 @@
         <v>87</v>
       </c>
       <c r="F230" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7129,9 +7821,12 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
         <v>73</v>
       </c>
-      <c r="G231" t="n">
+      <c r="H231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7158,9 +7853,12 @@
         <v>0</v>
       </c>
       <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
         <v>52</v>
       </c>
-      <c r="G232" t="n">
+      <c r="H232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7187,9 +7885,12 @@
         <v>0</v>
       </c>
       <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
         <v>35</v>
       </c>
-      <c r="G233" t="n">
+      <c r="H233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7216,9 +7917,12 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
         <v>35</v>
       </c>
-      <c r="G234" t="n">
+      <c r="H234" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7245,9 +7949,12 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
         <v>34</v>
       </c>
-      <c r="G235" t="n">
+      <c r="H235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7279,6 +7986,9 @@
       <c r="G236" t="n">
         <v>0</v>
       </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7308,6 +8018,9 @@
       <c r="G237" t="n">
         <v>0</v>
       </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7337,6 +8050,9 @@
       <c r="G238" t="n">
         <v>0</v>
       </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7366,6 +8082,9 @@
       <c r="G239" t="n">
         <v>0</v>
       </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7395,6 +8114,9 @@
       <c r="G240" t="n">
         <v>0</v>
       </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7424,6 +8146,9 @@
       <c r="G241" t="n">
         <v>0</v>
       </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7453,6 +8178,9 @@
       <c r="G242" t="n">
         <v>0</v>
       </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7482,6 +8210,9 @@
       <c r="G243" t="n">
         <v>0</v>
       </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7511,6 +8242,9 @@
       <c r="G244" t="n">
         <v>0</v>
       </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7540,6 +8274,9 @@
       <c r="G245" t="n">
         <v>0</v>
       </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7569,6 +8306,9 @@
       <c r="G246" t="n">
         <v>0</v>
       </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7598,6 +8338,9 @@
       <c r="G247" t="n">
         <v>0</v>
       </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7627,6 +8370,9 @@
       <c r="G248" t="n">
         <v>0</v>
       </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7656,6 +8402,9 @@
       <c r="G249" t="n">
         <v>0</v>
       </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7685,6 +8434,9 @@
       <c r="G250" t="n">
         <v>0</v>
       </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7714,6 +8466,9 @@
       <c r="G251" t="n">
         <v>0</v>
       </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7743,6 +8498,9 @@
       <c r="G252" t="n">
         <v>0</v>
       </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7772,6 +8530,9 @@
       <c r="G253" t="n">
         <v>0</v>
       </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7801,6 +8562,9 @@
       <c r="G254" t="n">
         <v>0</v>
       </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7830,6 +8594,9 @@
       <c r="G255" t="n">
         <v>0</v>
       </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7859,6 +8626,9 @@
       <c r="G256" t="n">
         <v>0</v>
       </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7888,6 +8658,9 @@
       <c r="G257" t="n">
         <v>0</v>
       </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7912,9 +8685,12 @@
         <v>204</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G258" t="n">
+        <v>197</v>
+      </c>
+      <c r="H258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7941,10 +8717,13 @@
         <v>208</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G259" t="n">
-        <v>4</v>
+        <v>197</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -7970,10 +8749,13 @@
         <v>208</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G260" t="n">
-        <v>2</v>
+        <v>199</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -7999,10 +8781,13 @@
         <v>208</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>200</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -8028,9 +8813,12 @@
         <v>208</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G262" t="n">
+        <v>201</v>
+      </c>
+      <c r="H262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8057,9 +8845,12 @@
         <v>208</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G263" t="n">
+        <v>201</v>
+      </c>
+      <c r="H263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8086,9 +8877,12 @@
         <v>208</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G264" t="n">
+        <v>202</v>
+      </c>
+      <c r="H264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8115,9 +8909,12 @@
         <v>208</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G265" t="n">
+        <v>202</v>
+      </c>
+      <c r="H265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8144,9 +8941,12 @@
         <v>208</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G266" t="n">
+        <v>202</v>
+      </c>
+      <c r="H266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8173,9 +8973,12 @@
         <v>208</v>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G267" t="n">
+        <v>202</v>
+      </c>
+      <c r="H267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8202,9 +9005,12 @@
         <v>208</v>
       </c>
       <c r="F268" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G268" t="n">
+        <v>202</v>
+      </c>
+      <c r="H268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8231,9 +9037,12 @@
         <v>208</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G269" t="n">
+        <v>201</v>
+      </c>
+      <c r="H269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8260,9 +9069,12 @@
         <v>205</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G270" t="n">
+        <v>198</v>
+      </c>
+      <c r="H270" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8289,9 +9101,12 @@
         <v>205</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G271" t="n">
+        <v>198</v>
+      </c>
+      <c r="H271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8318,9 +9133,12 @@
         <v>201</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G272" t="n">
+        <v>194</v>
+      </c>
+      <c r="H272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8347,9 +9165,12 @@
         <v>201</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G273" t="n">
+        <v>194</v>
+      </c>
+      <c r="H273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8376,9 +9197,12 @@
         <v>198</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G274" t="n">
+        <v>191</v>
+      </c>
+      <c r="H274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8405,9 +9229,12 @@
         <v>198</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G275" t="n">
+        <v>191</v>
+      </c>
+      <c r="H275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8439,6 +9266,9 @@
       <c r="G276" t="n">
         <v>0</v>
       </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8468,6 +9298,9 @@
       <c r="G277" t="n">
         <v>0</v>
       </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8497,6 +9330,9 @@
       <c r="G278" t="n">
         <v>0</v>
       </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8526,6 +9362,9 @@
       <c r="G279" t="n">
         <v>0</v>
       </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8555,6 +9394,9 @@
       <c r="G280" t="n">
         <v>0</v>
       </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8584,6 +9426,9 @@
       <c r="G281" t="n">
         <v>0</v>
       </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8613,6 +9458,9 @@
       <c r="G282" t="n">
         <v>0</v>
       </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8642,6 +9490,9 @@
       <c r="G283" t="n">
         <v>0</v>
       </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8671,6 +9522,9 @@
       <c r="G284" t="n">
         <v>0</v>
       </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8700,6 +9554,9 @@
       <c r="G285" t="n">
         <v>0</v>
       </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8729,6 +9586,9 @@
       <c r="G286" t="n">
         <v>0</v>
       </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8758,6 +9618,9 @@
       <c r="G287" t="n">
         <v>0</v>
       </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8787,6 +9650,9 @@
       <c r="G288" t="n">
         <v>0</v>
       </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8816,6 +9682,9 @@
       <c r="G289" t="n">
         <v>0</v>
       </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8845,6 +9714,9 @@
       <c r="G290" t="n">
         <v>0</v>
       </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8874,6 +9746,9 @@
       <c r="G291" t="n">
         <v>0</v>
       </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8903,6 +9778,9 @@
       <c r="G292" t="n">
         <v>0</v>
       </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8932,6 +9810,9 @@
       <c r="G293" t="n">
         <v>0</v>
       </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8961,6 +9842,9 @@
       <c r="G294" t="n">
         <v>0</v>
       </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8990,6 +9874,9 @@
       <c r="G295" t="n">
         <v>0</v>
       </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9019,6 +9906,9 @@
       <c r="G296" t="n">
         <v>0</v>
       </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9048,6 +9938,9 @@
       <c r="G297" t="n">
         <v>0</v>
       </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9077,6 +9970,9 @@
       <c r="G298" t="n">
         <v>0</v>
       </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9106,6 +10002,9 @@
       <c r="G299" t="n">
         <v>0</v>
       </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9135,6 +10034,9 @@
       <c r="G300" t="n">
         <v>0</v>
       </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9164,6 +10066,9 @@
       <c r="G301" t="n">
         <v>0</v>
       </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9193,6 +10098,9 @@
       <c r="G302" t="n">
         <v>0</v>
       </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9222,6 +10130,9 @@
       <c r="G303" t="n">
         <v>0</v>
       </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9251,6 +10162,9 @@
       <c r="G304" t="n">
         <v>0</v>
       </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9280,6 +10194,9 @@
       <c r="G305" t="n">
         <v>0</v>
       </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9307,6 +10224,9 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
+        <v>41</v>
+      </c>
+      <c r="H306" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9336,6 +10256,9 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
+        <v>41</v>
+      </c>
+      <c r="H307" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9365,7 +10288,10 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -9394,7 +10320,10 @@
         <v>0</v>
       </c>
       <c r="G309" t="n">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -9423,6 +10352,9 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
+        <v>42</v>
+      </c>
+      <c r="H310" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9452,6 +10384,9 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
+        <v>42</v>
+      </c>
+      <c r="H311" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9481,6 +10416,9 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
+        <v>42</v>
+      </c>
+      <c r="H312" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9510,6 +10448,9 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
+        <v>42</v>
+      </c>
+      <c r="H313" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9539,6 +10480,9 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
+        <v>42</v>
+      </c>
+      <c r="H314" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9568,6 +10512,9 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
+        <v>42</v>
+      </c>
+      <c r="H315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9597,6 +10544,9 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
+        <v>42</v>
+      </c>
+      <c r="H316" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9626,6 +10576,9 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
+        <v>42</v>
+      </c>
+      <c r="H317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9655,6 +10608,9 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
+        <v>42</v>
+      </c>
+      <c r="H318" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9684,6 +10640,9 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
+        <v>42</v>
+      </c>
+      <c r="H319" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9713,6 +10672,9 @@
         <v>0</v>
       </c>
       <c r="G320" t="n">
+        <v>42</v>
+      </c>
+      <c r="H320" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9742,6 +10704,9 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
+        <v>42</v>
+      </c>
+      <c r="H321" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9771,6 +10736,9 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
+        <v>42</v>
+      </c>
+      <c r="H322" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9800,6 +10768,9 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
+        <v>42</v>
+      </c>
+      <c r="H323" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9831,6 +10802,9 @@
       <c r="G324" t="n">
         <v>0</v>
       </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9860,6 +10834,9 @@
       <c r="G325" t="n">
         <v>0</v>
       </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9889,6 +10866,9 @@
       <c r="G326" t="n">
         <v>0</v>
       </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9918,6 +10898,9 @@
       <c r="G327" t="n">
         <v>0</v>
       </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9947,6 +10930,9 @@
       <c r="G328" t="n">
         <v>0</v>
       </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9976,6 +10962,9 @@
       <c r="G329" t="n">
         <v>0</v>
       </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10005,6 +10994,9 @@
       <c r="G330" t="n">
         <v>0</v>
       </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10034,6 +11026,9 @@
       <c r="G331" t="n">
         <v>0</v>
       </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10063,6 +11058,9 @@
       <c r="G332" t="n">
         <v>0</v>
       </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10092,6 +11090,9 @@
       <c r="G333" t="n">
         <v>0</v>
       </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -10121,6 +11122,9 @@
       <c r="G334" t="n">
         <v>0</v>
       </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -10150,6 +11154,9 @@
       <c r="G335" t="n">
         <v>0</v>
       </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -10179,6 +11186,9 @@
       <c r="G336" t="n">
         <v>0</v>
       </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -10206,6 +11216,9 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/CoberturaFinal.xlsx
+++ b/Result/CoberturaFinal.xlsx
@@ -938,13 +938,13 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1002,13 +1002,13 @@
         <v>380</v>
       </c>
       <c r="E18" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="F18" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G18" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>416</v>
       </c>
       <c r="E20" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="F20" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="G20" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1098,13 +1098,13 @@
         <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="F21" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="G21" t="n">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>463</v>
       </c>
       <c r="E22" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F22" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G22" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>463</v>
       </c>
       <c r="E23" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F23" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>465</v>
       </c>
       <c r="E24" t="n">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="F24" t="n">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="G24" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>501</v>
       </c>
       <c r="E25" t="n">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="F25" t="n">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>501</v>
       </c>
       <c r="E26" t="n">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="F26" t="n">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="G26" t="n">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>501</v>
       </c>
       <c r="E27" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F27" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G27" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>472</v>
       </c>
       <c r="E35" t="n">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F35" t="n">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G35" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>449</v>
       </c>
       <c r="E36" t="n">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="F36" t="n">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="G36" t="n">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>85</v>
       </c>
       <c r="E39" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F39" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G39" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         <v>37</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1770,13 +1770,13 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1802,13 +1802,13 @@
         <v>37</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>388</v>
       </c>
       <c r="E68" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="F68" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H68" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2634,16 +2634,16 @@
         <v>407</v>
       </c>
       <c r="E69" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="F69" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2666,13 +2666,13 @@
         <v>422</v>
       </c>
       <c r="E70" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F70" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2698,13 +2698,13 @@
         <v>423</v>
       </c>
       <c r="E71" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F71" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>427</v>
       </c>
       <c r="E72" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F72" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2762,13 +2762,13 @@
         <v>457</v>
       </c>
       <c r="E73" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F73" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G73" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>457</v>
       </c>
       <c r="E74" t="n">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="F74" t="n">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="G74" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>457</v>
       </c>
       <c r="E75" t="n">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="F75" t="n">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="G75" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2858,13 +2858,13 @@
         <v>458</v>
       </c>
       <c r="E76" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F76" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G76" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2890,13 +2890,13 @@
         <v>458</v>
       </c>
       <c r="E77" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F77" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G77" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2922,13 +2922,13 @@
         <v>455</v>
       </c>
       <c r="E78" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F78" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G78" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3082,13 +3082,13 @@
         <v>427</v>
       </c>
       <c r="E83" t="n">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F83" t="n">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="G83" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3114,13 +3114,13 @@
         <v>402</v>
       </c>
       <c r="E84" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="F84" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="G84" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>69</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G87" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G88" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>34</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G89" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         <v>34</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G90" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>32</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4074,13 +4074,13 @@
         <v>319</v>
       </c>
       <c r="E114" t="n">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="F114" t="n">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="G114" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>336</v>
       </c>
       <c r="E115" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F115" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4138,16 +4138,16 @@
         <v>347</v>
       </c>
       <c r="E116" t="n">
-        <v>411</v>
+        <v>347</v>
       </c>
       <c r="F116" t="n">
-        <v>411</v>
+        <v>347</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4170,16 +4170,16 @@
         <v>364</v>
       </c>
       <c r="E117" t="n">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="F117" t="n">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4202,16 +4202,16 @@
         <v>385</v>
       </c>
       <c r="E118" t="n">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="F118" t="n">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4266,13 +4266,13 @@
         <v>389</v>
       </c>
       <c r="E120" t="n">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F120" t="n">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -4298,13 +4298,13 @@
         <v>413</v>
       </c>
       <c r="E121" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F121" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G121" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4330,13 +4330,13 @@
         <v>411</v>
       </c>
       <c r="E122" t="n">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="F122" t="n">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="G122" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4362,13 +4362,13 @@
         <v>411</v>
       </c>
       <c r="E123" t="n">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F123" t="n">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -4394,13 +4394,13 @@
         <v>413</v>
       </c>
       <c r="E124" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F124" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4426,13 +4426,13 @@
         <v>413</v>
       </c>
       <c r="E125" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F125" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>409</v>
       </c>
       <c r="E129" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F129" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="G129" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4650,13 +4650,13 @@
         <v>359</v>
       </c>
       <c r="E132" t="n">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="F132" t="n">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="G132" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4746,13 +4746,13 @@
         <v>66</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G135" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4778,13 +4778,13 @@
         <v>48</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G136" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4810,13 +4810,13 @@
         <v>30</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G137" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4842,13 +4842,13 @@
         <v>29</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G138" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4874,13 +4874,13 @@
         <v>27</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G139" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G160" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5610,13 +5610,13 @@
         <v>362</v>
       </c>
       <c r="E162" t="n">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="F162" t="n">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="G162" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5674,16 +5674,16 @@
         <v>391</v>
       </c>
       <c r="E164" t="n">
-        <v>418</v>
+        <v>356</v>
       </c>
       <c r="F164" t="n">
-        <v>418</v>
+        <v>356</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H164" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -5706,16 +5706,16 @@
         <v>408</v>
       </c>
       <c r="E165" t="n">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="F165" t="n">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H165" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -5738,13 +5738,13 @@
         <v>428</v>
       </c>
       <c r="E166" t="n">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="F166" t="n">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="G166" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>428</v>
       </c>
       <c r="E167" t="n">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="F167" t="n">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G167" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5802,13 +5802,13 @@
         <v>429</v>
       </c>
       <c r="E168" t="n">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="F168" t="n">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="G168" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>453</v>
       </c>
       <c r="E169" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F169" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G169" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>454</v>
       </c>
       <c r="E170" t="n">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="F170" t="n">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="G170" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5898,13 +5898,13 @@
         <v>454</v>
       </c>
       <c r="E171" t="n">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="F171" t="n">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="G171" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5962,13 +5962,13 @@
         <v>454</v>
       </c>
       <c r="E173" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F173" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G173" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         <v>451</v>
       </c>
       <c r="E174" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F174" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G174" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -6154,13 +6154,13 @@
         <v>430</v>
       </c>
       <c r="E179" t="n">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F179" t="n">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G179" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -6186,13 +6186,13 @@
         <v>390</v>
       </c>
       <c r="E180" t="n">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="F180" t="n">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="G180" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         <v>62</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G183" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -6314,13 +6314,13 @@
         <v>45</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G184" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>27</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G185" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -6378,13 +6378,13 @@
         <v>27</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G186" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -6410,13 +6410,13 @@
         <v>26</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G187" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>6</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G208" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -7146,13 +7146,13 @@
         <v>367</v>
       </c>
       <c r="E210" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F210" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G210" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -7210,16 +7210,16 @@
         <v>402</v>
       </c>
       <c r="E212" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="F212" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H212" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -7242,13 +7242,13 @@
         <v>422</v>
       </c>
       <c r="E213" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="F213" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="G213" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7274,13 +7274,13 @@
         <v>438</v>
       </c>
       <c r="E214" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F214" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G214" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -7306,13 +7306,13 @@
         <v>438</v>
       </c>
       <c r="E215" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F215" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G215" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>440</v>
       </c>
       <c r="E216" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F216" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G216" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7402,13 +7402,13 @@
         <v>472</v>
       </c>
       <c r="E218" t="n">
-        <v>412</v>
+        <v>318</v>
       </c>
       <c r="F218" t="n">
-        <v>412</v>
+        <v>318</v>
       </c>
       <c r="G218" t="n">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -7434,13 +7434,13 @@
         <v>472</v>
       </c>
       <c r="E219" t="n">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="F219" t="n">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="G219" t="n">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7466,13 +7466,13 @@
         <v>473</v>
       </c>
       <c r="E220" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F220" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G220" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7498,13 +7498,13 @@
         <v>473</v>
       </c>
       <c r="E221" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F221" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G221" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -7530,13 +7530,13 @@
         <v>472</v>
       </c>
       <c r="E222" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F222" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G222" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>471</v>
       </c>
       <c r="E223" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F223" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G223" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -7594,13 +7594,13 @@
         <v>468</v>
       </c>
       <c r="E224" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F224" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G224" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7690,13 +7690,13 @@
         <v>431</v>
       </c>
       <c r="E227" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F227" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G227" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>73</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G231" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7850,13 +7850,13 @@
         <v>52</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G232" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7882,13 +7882,13 @@
         <v>35</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G233" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>35</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G234" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7946,13 +7946,13 @@
         <v>34</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G235" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -8685,10 +8685,10 @@
         <v>204</v>
       </c>
       <c r="F258" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -8714,13 +8714,13 @@
         <v>204</v>
       </c>
       <c r="E259" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F259" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -8749,10 +8749,10 @@
         <v>208</v>
       </c>
       <c r="F260" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -8781,10 +8781,10 @@
         <v>208</v>
       </c>
       <c r="F261" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -8813,10 +8813,10 @@
         <v>208</v>
       </c>
       <c r="F262" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8845,10 +8845,10 @@
         <v>208</v>
       </c>
       <c r="F263" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8877,10 +8877,10 @@
         <v>208</v>
       </c>
       <c r="F264" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8909,10 +8909,10 @@
         <v>208</v>
       </c>
       <c r="F265" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8941,10 +8941,10 @@
         <v>208</v>
       </c>
       <c r="F266" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8973,10 +8973,10 @@
         <v>208</v>
       </c>
       <c r="F267" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -9005,10 +9005,10 @@
         <v>208</v>
       </c>
       <c r="F268" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -9037,10 +9037,10 @@
         <v>208</v>
       </c>
       <c r="F269" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -9069,10 +9069,10 @@
         <v>205</v>
       </c>
       <c r="F270" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -9101,10 +9101,10 @@
         <v>205</v>
       </c>
       <c r="F271" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>201</v>
       </c>
       <c r="F272" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -9165,10 +9165,10 @@
         <v>201</v>
       </c>
       <c r="F273" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>198</v>
       </c>
       <c r="F274" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -9229,10 +9229,10 @@
         <v>198</v>
       </c>
       <c r="F275" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>

--- a/Result/CoberturaFinal.xlsx
+++ b/Result/CoberturaFinal.xlsx
@@ -1066,13 +1066,13 @@
         <v>416</v>
       </c>
       <c r="E20" t="n">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="F20" t="n">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="G20" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1098,13 +1098,13 @@
         <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="F21" t="n">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="G21" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>463</v>
       </c>
       <c r="E23" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F23" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>465</v>
       </c>
       <c r="E24" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="F24" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="G24" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>501</v>
       </c>
       <c r="E25" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="F25" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="G25" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>501</v>
       </c>
       <c r="E26" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F26" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G26" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>501</v>
       </c>
       <c r="E27" t="n">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="F27" t="n">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="G27" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1322,13 +1322,13 @@
         <v>502</v>
       </c>
       <c r="E28" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F28" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G28" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>85</v>
       </c>
       <c r="E39" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F39" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G39" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1770,13 +1770,13 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1802,13 +1802,13 @@
         <v>37</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2570,13 +2570,13 @@
         <v>374</v>
       </c>
       <c r="E67" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F67" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G67" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>388</v>
       </c>
       <c r="E68" t="n">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="F68" t="n">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G68" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2634,13 +2634,13 @@
         <v>407</v>
       </c>
       <c r="E69" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F69" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G69" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2666,13 +2666,13 @@
         <v>422</v>
       </c>
       <c r="E70" t="n">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="F70" t="n">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="G70" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2698,13 +2698,13 @@
         <v>423</v>
       </c>
       <c r="E71" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F71" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>427</v>
       </c>
       <c r="E72" t="n">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="F72" t="n">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="G72" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2762,13 +2762,13 @@
         <v>457</v>
       </c>
       <c r="E73" t="n">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="F73" t="n">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="G73" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>457</v>
       </c>
       <c r="E74" t="n">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="F74" t="n">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="G74" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>457</v>
       </c>
       <c r="E75" t="n">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="F75" t="n">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="G75" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2858,13 +2858,13 @@
         <v>458</v>
       </c>
       <c r="E76" t="n">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F76" t="n">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G76" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2890,13 +2890,13 @@
         <v>458</v>
       </c>
       <c r="E77" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F77" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G77" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2922,13 +2922,13 @@
         <v>455</v>
       </c>
       <c r="E78" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F78" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G78" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F86" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>69</v>
       </c>
       <c r="E87" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F87" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G87" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F88" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>34</v>
       </c>
       <c r="E89" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F89" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         <v>34</v>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>32</v>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4266,13 +4266,13 @@
         <v>389</v>
       </c>
       <c r="E120" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F120" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="G120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -4298,13 +4298,13 @@
         <v>413</v>
       </c>
       <c r="E121" t="n">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="F121" t="n">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="G121" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4330,13 +4330,13 @@
         <v>411</v>
       </c>
       <c r="E122" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="F122" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="G122" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4362,13 +4362,13 @@
         <v>411</v>
       </c>
       <c r="E123" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F123" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="G123" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -4394,13 +4394,13 @@
         <v>413</v>
       </c>
       <c r="E124" t="n">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F124" t="n">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4874,13 +4874,13 @@
         <v>27</v>
       </c>
       <c r="E139" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F139" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
         <v>7</v>
-      </c>
-      <c r="F160" t="n">
-        <v>7</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5610,13 +5610,13 @@
         <v>362</v>
       </c>
       <c r="E162" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F162" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="G162" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5674,13 +5674,13 @@
         <v>391</v>
       </c>
       <c r="E164" t="n">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F164" t="n">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="G164" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5706,13 +5706,13 @@
         <v>408</v>
       </c>
       <c r="E165" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="F165" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="G165" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5802,13 +5802,13 @@
         <v>429</v>
       </c>
       <c r="E168" t="n">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="F168" t="n">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="G168" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>453</v>
       </c>
       <c r="E169" t="n">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F169" t="n">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="G169" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>454</v>
       </c>
       <c r="E170" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F170" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G170" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5898,13 +5898,13 @@
         <v>454</v>
       </c>
       <c r="E171" t="n">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F171" t="n">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="G171" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5930,13 +5930,13 @@
         <v>454</v>
       </c>
       <c r="E172" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F172" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G172" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5962,13 +5962,13 @@
         <v>454</v>
       </c>
       <c r="E173" t="n">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="F173" t="n">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G173" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         <v>451</v>
       </c>
       <c r="E174" t="n">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="F174" t="n">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G174" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -6026,13 +6026,13 @@
         <v>451</v>
       </c>
       <c r="E175" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F175" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G175" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -6154,13 +6154,13 @@
         <v>430</v>
       </c>
       <c r="E179" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F179" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G179" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         <v>62</v>
       </c>
       <c r="E183" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F183" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -6314,13 +6314,13 @@
         <v>45</v>
       </c>
       <c r="E184" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F184" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -7210,13 +7210,13 @@
         <v>402</v>
       </c>
       <c r="E212" t="n">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="F212" t="n">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="G212" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -7242,13 +7242,13 @@
         <v>422</v>
       </c>
       <c r="E213" t="n">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="F213" t="n">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="G213" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7274,13 +7274,13 @@
         <v>438</v>
       </c>
       <c r="E214" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F214" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="G214" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -7306,13 +7306,13 @@
         <v>438</v>
       </c>
       <c r="E215" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F215" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G215" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>440</v>
       </c>
       <c r="E216" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F216" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G216" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7402,13 +7402,13 @@
         <v>472</v>
       </c>
       <c r="E218" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F218" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G218" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -7434,13 +7434,13 @@
         <v>472</v>
       </c>
       <c r="E219" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F219" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G219" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>73</v>
       </c>
       <c r="E231" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F231" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G231" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7850,13 +7850,13 @@
         <v>52</v>
       </c>
       <c r="E232" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F232" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G232" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7882,13 +7882,13 @@
         <v>35</v>
       </c>
       <c r="E233" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F233" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G233" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>35</v>
       </c>
       <c r="E234" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7946,13 +7946,13 @@
         <v>34</v>
       </c>
       <c r="E235" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>

--- a/Result/CoberturaFinal.xlsx
+++ b/Result/CoberturaFinal.xlsx
@@ -938,13 +938,13 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1002,13 +1002,13 @@
         <v>380</v>
       </c>
       <c r="E18" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F18" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G18" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1034,13 +1034,13 @@
         <v>400</v>
       </c>
       <c r="E19" t="n">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="F19" t="n">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="G19" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>416</v>
       </c>
       <c r="E20" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="F20" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="G20" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1098,13 +1098,13 @@
         <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="F21" t="n">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="G21" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>463</v>
       </c>
       <c r="E22" t="n">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="F22" t="n">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="G22" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>463</v>
       </c>
       <c r="E23" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F23" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>465</v>
       </c>
       <c r="E24" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F24" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G24" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>501</v>
       </c>
       <c r="E26" t="n">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="F26" t="n">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="G26" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>501</v>
       </c>
       <c r="E27" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F27" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G27" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1322,13 +1322,13 @@
         <v>502</v>
       </c>
       <c r="E28" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F28" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G28" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>472</v>
       </c>
       <c r="E35" t="n">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F35" t="n">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="G35" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>449</v>
       </c>
       <c r="E36" t="n">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="F36" t="n">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="G36" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>85</v>
       </c>
       <c r="E39" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F39" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         <v>37</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1770,13 +1770,13 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1802,13 +1802,13 @@
         <v>37</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2538,13 +2538,13 @@
         <v>360</v>
       </c>
       <c r="E66" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F66" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G66" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2570,13 +2570,13 @@
         <v>374</v>
       </c>
       <c r="E67" t="n">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="F67" t="n">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="G67" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>388</v>
       </c>
       <c r="E68" t="n">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="F68" t="n">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="G68" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2634,13 +2634,13 @@
         <v>407</v>
       </c>
       <c r="E69" t="n">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="F69" t="n">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="G69" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2666,13 +2666,13 @@
         <v>422</v>
       </c>
       <c r="E70" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F70" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="G70" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2698,13 +2698,13 @@
         <v>423</v>
       </c>
       <c r="E71" t="n">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="F71" t="n">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="G71" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>427</v>
       </c>
       <c r="E72" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F72" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2762,13 +2762,13 @@
         <v>457</v>
       </c>
       <c r="E73" t="n">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F73" t="n">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G73" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>457</v>
       </c>
       <c r="E74" t="n">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="F74" t="n">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G74" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>457</v>
       </c>
       <c r="E75" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="F75" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="G75" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2858,13 +2858,13 @@
         <v>458</v>
       </c>
       <c r="E76" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F76" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G76" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3082,13 +3082,13 @@
         <v>427</v>
       </c>
       <c r="E83" t="n">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F83" t="n">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="G83" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3114,13 +3114,13 @@
         <v>402</v>
       </c>
       <c r="E84" t="n">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="F84" t="n">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="G84" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>69</v>
       </c>
       <c r="E87" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="F87" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>34</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         <v>34</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G90" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>32</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G91" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4074,13 +4074,13 @@
         <v>319</v>
       </c>
       <c r="E114" t="n">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="F114" t="n">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="G114" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>336</v>
       </c>
       <c r="E115" t="n">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="F115" t="n">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4330,13 +4330,13 @@
         <v>411</v>
       </c>
       <c r="E122" t="n">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="F122" t="n">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="G122" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4362,13 +4362,13 @@
         <v>411</v>
       </c>
       <c r="E123" t="n">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="F123" t="n">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="G123" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -4394,13 +4394,13 @@
         <v>413</v>
       </c>
       <c r="E124" t="n">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="F124" t="n">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="G124" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4426,13 +4426,13 @@
         <v>413</v>
       </c>
       <c r="E125" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F125" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4650,13 +4650,13 @@
         <v>359</v>
       </c>
       <c r="E132" t="n">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="F132" t="n">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4842,13 +4842,13 @@
         <v>29</v>
       </c>
       <c r="E138" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F138" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4874,13 +4874,13 @@
         <v>27</v>
       </c>
       <c r="E139" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F139" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G160" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5610,13 +5610,13 @@
         <v>362</v>
       </c>
       <c r="E162" t="n">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="F162" t="n">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="G162" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5642,13 +5642,13 @@
         <v>376</v>
       </c>
       <c r="E163" t="n">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="F163" t="n">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="G163" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5674,13 +5674,13 @@
         <v>391</v>
       </c>
       <c r="E164" t="n">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="F164" t="n">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="G164" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5706,13 +5706,13 @@
         <v>408</v>
       </c>
       <c r="E165" t="n">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F165" t="n">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G165" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5738,13 +5738,13 @@
         <v>428</v>
       </c>
       <c r="E166" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F166" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="G166" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>428</v>
       </c>
       <c r="E167" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F167" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G167" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5802,13 +5802,13 @@
         <v>429</v>
       </c>
       <c r="E168" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F168" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G168" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>453</v>
       </c>
       <c r="E169" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F169" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G169" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>454</v>
       </c>
       <c r="E170" t="n">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="F170" t="n">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="G170" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5898,13 +5898,13 @@
         <v>454</v>
       </c>
       <c r="E171" t="n">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F171" t="n">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="G171" t="n">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5930,13 +5930,13 @@
         <v>454</v>
       </c>
       <c r="E172" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F172" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G172" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5962,13 +5962,13 @@
         <v>454</v>
       </c>
       <c r="E173" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="F173" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="G173" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         <v>451</v>
       </c>
       <c r="E174" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="F174" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="G174" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -6026,13 +6026,13 @@
         <v>451</v>
       </c>
       <c r="E175" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F175" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G175" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -6154,13 +6154,13 @@
         <v>430</v>
       </c>
       <c r="E179" t="n">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="F179" t="n">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="G179" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         <v>62</v>
       </c>
       <c r="E183" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F183" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G183" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -6314,13 +6314,13 @@
         <v>45</v>
       </c>
       <c r="E184" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F184" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G184" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>27</v>
       </c>
       <c r="E185" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F185" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -6378,13 +6378,13 @@
         <v>27</v>
       </c>
       <c r="E186" t="n">
+        <v>15</v>
+      </c>
+      <c r="F186" t="n">
+        <v>15</v>
+      </c>
+      <c r="G186" t="n">
         <v>12</v>
-      </c>
-      <c r="F186" t="n">
-        <v>12</v>
-      </c>
-      <c r="G186" t="n">
-        <v>15</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -6410,13 +6410,13 @@
         <v>26</v>
       </c>
       <c r="E187" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G187" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>6</v>
       </c>
       <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
         <v>6</v>
-      </c>
-      <c r="F208" t="n">
-        <v>6</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -7146,13 +7146,13 @@
         <v>367</v>
       </c>
       <c r="E210" t="n">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="F210" t="n">
-        <v>277</v>
+        <v>97</v>
       </c>
       <c r="G210" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -7178,13 +7178,13 @@
         <v>385</v>
       </c>
       <c r="E211" t="n">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="F211" t="n">
-        <v>331</v>
+        <v>118</v>
       </c>
       <c r="G211" t="n">
-        <v>54</v>
+        <v>267</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -7210,13 +7210,13 @@
         <v>402</v>
       </c>
       <c r="E212" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="F212" t="n">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="G212" t="n">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -7242,13 +7242,13 @@
         <v>422</v>
       </c>
       <c r="E213" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="F213" t="n">
-        <v>366</v>
+        <v>238</v>
       </c>
       <c r="G213" t="n">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7274,13 +7274,13 @@
         <v>438</v>
       </c>
       <c r="E214" t="n">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F214" t="n">
-        <v>396</v>
+        <v>238</v>
       </c>
       <c r="G214" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -7306,13 +7306,13 @@
         <v>438</v>
       </c>
       <c r="E215" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F215" t="n">
-        <v>408</v>
+        <v>238</v>
       </c>
       <c r="G215" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>440</v>
       </c>
       <c r="E216" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F216" t="n">
-        <v>408</v>
+        <v>238</v>
       </c>
       <c r="G216" t="n">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7373,10 +7373,10 @@
         <v>418</v>
       </c>
       <c r="F217" t="n">
-        <v>418</v>
+        <v>250</v>
       </c>
       <c r="G217" t="n">
-        <v>54</v>
+        <v>222</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -7402,13 +7402,13 @@
         <v>472</v>
       </c>
       <c r="E218" t="n">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="F218" t="n">
-        <v>313</v>
+        <v>195</v>
       </c>
       <c r="G218" t="n">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -7434,13 +7434,13 @@
         <v>472</v>
       </c>
       <c r="E219" t="n">
-        <v>313</v>
+        <v>405</v>
       </c>
       <c r="F219" t="n">
-        <v>313</v>
+        <v>237</v>
       </c>
       <c r="G219" t="n">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7466,13 +7466,13 @@
         <v>473</v>
       </c>
       <c r="E220" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="F220" t="n">
-        <v>388</v>
+        <v>250</v>
       </c>
       <c r="G220" t="n">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7498,13 +7498,13 @@
         <v>473</v>
       </c>
       <c r="E221" t="n">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="F221" t="n">
-        <v>388</v>
+        <v>250</v>
       </c>
       <c r="G221" t="n">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -7530,13 +7530,13 @@
         <v>472</v>
       </c>
       <c r="E222" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F222" t="n">
-        <v>403</v>
+        <v>250</v>
       </c>
       <c r="G222" t="n">
-        <v>69</v>
+        <v>222</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>471</v>
       </c>
       <c r="E223" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F223" t="n">
-        <v>403</v>
+        <v>250</v>
       </c>
       <c r="G223" t="n">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -7594,13 +7594,13 @@
         <v>468</v>
       </c>
       <c r="E224" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F224" t="n">
-        <v>403</v>
+        <v>250</v>
       </c>
       <c r="G224" t="n">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7629,10 +7629,10 @@
         <v>418</v>
       </c>
       <c r="F225" t="n">
-        <v>418</v>
+        <v>250</v>
       </c>
       <c r="G225" t="n">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -7661,10 +7661,10 @@
         <v>418</v>
       </c>
       <c r="F226" t="n">
-        <v>418</v>
+        <v>250</v>
       </c>
       <c r="G226" t="n">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -7690,13 +7690,13 @@
         <v>431</v>
       </c>
       <c r="E227" t="n">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="F227" t="n">
-        <v>412</v>
+        <v>250</v>
       </c>
       <c r="G227" t="n">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>216</v>
       </c>
       <c r="F228" t="n">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>73</v>
       </c>
       <c r="E231" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="F231" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G231" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7850,13 +7850,13 @@
         <v>52</v>
       </c>
       <c r="E232" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F232" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7882,13 +7882,13 @@
         <v>35</v>
       </c>
       <c r="E233" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F233" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G233" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>35</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G234" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7946,13 +7946,13 @@
         <v>34</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G235" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -8685,10 +8685,10 @@
         <v>204</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G258" t="n">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -8717,10 +8717,10 @@
         <v>204</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G259" t="n">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -8746,13 +8746,13 @@
         <v>206</v>
       </c>
       <c r="E260" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="G260" t="n">
-        <v>206</v>
+        <v>60</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -8778,13 +8778,13 @@
         <v>207</v>
       </c>
       <c r="E261" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G261" t="n">
-        <v>207</v>
+        <v>60</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -8813,10 +8813,10 @@
         <v>208</v>
       </c>
       <c r="F262" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G262" t="n">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8845,10 +8845,10 @@
         <v>208</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G263" t="n">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>209</v>
       </c>
       <c r="E264" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G264" t="n">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8906,13 +8906,13 @@
         <v>209</v>
       </c>
       <c r="E265" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G265" t="n">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8938,13 +8938,13 @@
         <v>209</v>
       </c>
       <c r="E266" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G266" t="n">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8970,13 +8970,13 @@
         <v>209</v>
       </c>
       <c r="E267" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G267" t="n">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -9002,13 +9002,13 @@
         <v>209</v>
       </c>
       <c r="E268" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G268" t="n">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -9037,10 +9037,10 @@
         <v>208</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="G269" t="n">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -9069,10 +9069,10 @@
         <v>205</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="G270" t="n">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -9101,10 +9101,10 @@
         <v>205</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="G271" t="n">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>201</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G272" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -9165,10 +9165,10 @@
         <v>201</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G273" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>198</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G274" t="n">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -9229,10 +9229,10 @@
         <v>198</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G275" t="n">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -10221,10 +10221,10 @@
         <v>41</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G306" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -10253,10 +10253,10 @@
         <v>41</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G307" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -10282,13 +10282,13 @@
         <v>41</v>
       </c>
       <c r="E308" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G308" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -10314,13 +10314,13 @@
         <v>41</v>
       </c>
       <c r="E309" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G309" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -10349,10 +10349,10 @@
         <v>42</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G310" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -10381,10 +10381,10 @@
         <v>42</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G311" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -10413,10 +10413,10 @@
         <v>42</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G312" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -10445,10 +10445,10 @@
         <v>42</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G313" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -10477,10 +10477,10 @@
         <v>42</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G314" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -10509,10 +10509,10 @@
         <v>42</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G315" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -10541,10 +10541,10 @@
         <v>42</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G316" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -10573,10 +10573,10 @@
         <v>42</v>
       </c>
       <c r="F317" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G317" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -10605,10 +10605,10 @@
         <v>42</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G318" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -10637,10 +10637,10 @@
         <v>42</v>
       </c>
       <c r="F319" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G319" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -10669,10 +10669,10 @@
         <v>42</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G320" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -10701,10 +10701,10 @@
         <v>42</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G321" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -10733,10 +10733,10 @@
         <v>42</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G322" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -10765,10 +10765,10 @@
         <v>42</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G323" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>

--- a/Result/CoberturaFinal.xlsx
+++ b/Result/CoberturaFinal.xlsx
@@ -938,16 +938,16 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -970,16 +970,16 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1002,13 +1002,13 @@
         <v>380</v>
       </c>
       <c r="E18" t="n">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="G18" t="n">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1034,13 +1034,13 @@
         <v>400</v>
       </c>
       <c r="E19" t="n">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="F19" t="n">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="G19" t="n">
-        <v>121</v>
+        <v>247</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>416</v>
       </c>
       <c r="E20" t="n">
-        <v>363</v>
+        <v>248</v>
       </c>
       <c r="F20" t="n">
-        <v>363</v>
+        <v>248</v>
       </c>
       <c r="G20" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1098,13 +1098,13 @@
         <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>393</v>
+        <v>298</v>
       </c>
       <c r="F21" t="n">
-        <v>393</v>
+        <v>298</v>
       </c>
       <c r="G21" t="n">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>463</v>
       </c>
       <c r="E22" t="n">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="F22" t="n">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>463</v>
       </c>
       <c r="E23" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F23" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
         <v>465</v>
       </c>
       <c r="E24" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F24" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="G24" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>501</v>
       </c>
       <c r="E25" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F25" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>501</v>
       </c>
       <c r="E26" t="n">
-        <v>343</v>
+        <v>388</v>
       </c>
       <c r="F26" t="n">
-        <v>343</v>
+        <v>388</v>
       </c>
       <c r="G26" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>501</v>
       </c>
       <c r="E27" t="n">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="F27" t="n">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="G27" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1482,13 +1482,13 @@
         <v>497</v>
       </c>
       <c r="E33" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F33" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G33" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1514,13 +1514,13 @@
         <v>488</v>
       </c>
       <c r="E34" t="n">
-        <v>418</v>
+        <v>343</v>
       </c>
       <c r="F34" t="n">
-        <v>418</v>
+        <v>343</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>472</v>
       </c>
       <c r="E35" t="n">
-        <v>415</v>
+        <v>280</v>
       </c>
       <c r="F35" t="n">
-        <v>415</v>
+        <v>280</v>
       </c>
       <c r="G35" t="n">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>449</v>
       </c>
       <c r="E36" t="n">
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="F36" t="n">
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="G36" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1610,16 +1610,16 @@
         <v>121</v>
       </c>
       <c r="E37" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="F37" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -1674,13 +1674,13 @@
         <v>85</v>
       </c>
       <c r="E39" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F39" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G39" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G40" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1738,13 +1738,13 @@
         <v>37</v>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1770,13 +1770,13 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1802,13 +1802,13 @@
         <v>37</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2474,16 +2474,16 @@
         <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G64" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         <v>17</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="F65" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
@@ -2538,13 +2538,13 @@
         <v>360</v>
       </c>
       <c r="E66" t="n">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="F66" t="n">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="G66" t="n">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2570,13 +2570,13 @@
         <v>374</v>
       </c>
       <c r="E67" t="n">
-        <v>287</v>
+        <v>165</v>
       </c>
       <c r="F67" t="n">
-        <v>287</v>
+        <v>165</v>
       </c>
       <c r="G67" t="n">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>388</v>
       </c>
       <c r="E68" t="n">
-        <v>382</v>
+        <v>260</v>
       </c>
       <c r="F68" t="n">
-        <v>382</v>
+        <v>260</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2634,13 +2634,13 @@
         <v>407</v>
       </c>
       <c r="E69" t="n">
-        <v>407</v>
+        <v>310</v>
       </c>
       <c r="F69" t="n">
-        <v>407</v>
+        <v>310</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2666,13 +2666,13 @@
         <v>422</v>
       </c>
       <c r="E70" t="n">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="F70" t="n">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2698,13 +2698,13 @@
         <v>423</v>
       </c>
       <c r="E71" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F71" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G71" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>427</v>
       </c>
       <c r="E72" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F72" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G72" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2762,13 +2762,13 @@
         <v>457</v>
       </c>
       <c r="E73" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F73" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G73" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>457</v>
       </c>
       <c r="E74" t="n">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="F74" t="n">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="G74" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>457</v>
       </c>
       <c r="E75" t="n">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="F75" t="n">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="G75" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3018,13 +3018,13 @@
         <v>453</v>
       </c>
       <c r="E81" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F81" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G81" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3050,13 +3050,13 @@
         <v>442</v>
       </c>
       <c r="E82" t="n">
-        <v>418</v>
+        <v>343</v>
       </c>
       <c r="F82" t="n">
-        <v>418</v>
+        <v>343</v>
       </c>
       <c r="G82" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3082,13 +3082,13 @@
         <v>427</v>
       </c>
       <c r="E83" t="n">
-        <v>416</v>
+        <v>268</v>
       </c>
       <c r="F83" t="n">
-        <v>416</v>
+        <v>268</v>
       </c>
       <c r="G83" t="n">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3114,13 +3114,13 @@
         <v>402</v>
       </c>
       <c r="E84" t="n">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="F84" t="n">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="G84" t="n">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3146,16 +3146,16 @@
         <v>95</v>
       </c>
       <c r="E85" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="F85" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86">
@@ -3178,16 +3178,16 @@
         <v>81</v>
       </c>
       <c r="E86" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F86" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -3210,13 +3210,13 @@
         <v>69</v>
       </c>
       <c r="E87" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="F87" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="G87" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3242,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>34</v>
       </c>
       <c r="E89" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G89" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         <v>34</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>32</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4010,16 +4010,16 @@
         <v>11</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F112" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -4042,16 +4042,16 @@
         <v>17</v>
       </c>
       <c r="E113" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F113" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114">
@@ -4074,13 +4074,13 @@
         <v>319</v>
       </c>
       <c r="E114" t="n">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="F114" t="n">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="G114" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>336</v>
       </c>
       <c r="E115" t="n">
-        <v>310</v>
+        <v>168</v>
       </c>
       <c r="F115" t="n">
-        <v>310</v>
+        <v>168</v>
       </c>
       <c r="G115" t="n">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4138,13 +4138,13 @@
         <v>347</v>
       </c>
       <c r="E116" t="n">
-        <v>347</v>
+        <v>263</v>
       </c>
       <c r="F116" t="n">
-        <v>347</v>
+        <v>263</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -4170,13 +4170,13 @@
         <v>364</v>
       </c>
       <c r="E117" t="n">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="F117" t="n">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4202,13 +4202,13 @@
         <v>385</v>
       </c>
       <c r="E118" t="n">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="F118" t="n">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -4298,13 +4298,13 @@
         <v>413</v>
       </c>
       <c r="E121" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F121" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4330,13 +4330,13 @@
         <v>411</v>
       </c>
       <c r="E122" t="n">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="F122" t="n">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="G122" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4362,13 +4362,13 @@
         <v>411</v>
       </c>
       <c r="E123" t="n">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="F123" t="n">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="G123" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -4426,13 +4426,13 @@
         <v>413</v>
       </c>
       <c r="E125" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F125" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4490,13 +4490,13 @@
         <v>411</v>
       </c>
       <c r="E127" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F127" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>409</v>
       </c>
       <c r="E129" t="n">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="F129" t="n">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4586,13 +4586,13 @@
         <v>398</v>
       </c>
       <c r="E130" t="n">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="F130" t="n">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4618,13 +4618,13 @@
         <v>381</v>
       </c>
       <c r="E131" t="n">
-        <v>381</v>
+        <v>265</v>
       </c>
       <c r="F131" t="n">
-        <v>381</v>
+        <v>265</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4650,13 +4650,13 @@
         <v>359</v>
       </c>
       <c r="E132" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="F132" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="G132" t="n">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4682,16 +4682,16 @@
         <v>95</v>
       </c>
       <c r="E133" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F133" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
@@ -4746,13 +4746,13 @@
         <v>66</v>
       </c>
       <c r="E135" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F135" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4778,13 +4778,13 @@
         <v>48</v>
       </c>
       <c r="E136" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F136" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -5514,13 +5514,13 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5546,16 +5546,16 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F160" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161">
@@ -5578,16 +5578,16 @@
         <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F161" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="162">
@@ -5610,13 +5610,13 @@
         <v>362</v>
       </c>
       <c r="E162" t="n">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="F162" t="n">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="G162" t="n">
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5642,13 +5642,13 @@
         <v>376</v>
       </c>
       <c r="E163" t="n">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="F163" t="n">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="G163" t="n">
-        <v>51</v>
+        <v>245</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5674,13 +5674,13 @@
         <v>391</v>
       </c>
       <c r="E164" t="n">
-        <v>356</v>
+        <v>251</v>
       </c>
       <c r="F164" t="n">
-        <v>356</v>
+        <v>251</v>
       </c>
       <c r="G164" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5706,13 +5706,13 @@
         <v>408</v>
       </c>
       <c r="E165" t="n">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="F165" t="n">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="G165" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5738,13 +5738,13 @@
         <v>428</v>
       </c>
       <c r="E166" t="n">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="F166" t="n">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="G166" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>428</v>
       </c>
       <c r="E167" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F167" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G167" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5802,13 +5802,13 @@
         <v>429</v>
       </c>
       <c r="E168" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F168" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G168" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>454</v>
       </c>
       <c r="E170" t="n">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="F170" t="n">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="G170" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5898,13 +5898,13 @@
         <v>454</v>
       </c>
       <c r="E171" t="n">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="F171" t="n">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="G171" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5930,13 +5930,13 @@
         <v>454</v>
       </c>
       <c r="E172" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F172" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G172" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5962,13 +5962,13 @@
         <v>454</v>
       </c>
       <c r="E173" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F173" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G173" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         <v>451</v>
       </c>
       <c r="E174" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="F174" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G174" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -6122,13 +6122,13 @@
         <v>442</v>
       </c>
       <c r="E178" t="n">
-        <v>418</v>
+        <v>357</v>
       </c>
       <c r="F178" t="n">
-        <v>418</v>
+        <v>357</v>
       </c>
       <c r="G178" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -6154,13 +6154,13 @@
         <v>430</v>
       </c>
       <c r="E179" t="n">
-        <v>396</v>
+        <v>302</v>
       </c>
       <c r="F179" t="n">
-        <v>396</v>
+        <v>302</v>
       </c>
       <c r="G179" t="n">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -6186,13 +6186,13 @@
         <v>390</v>
       </c>
       <c r="E180" t="n">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="F180" t="n">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="G180" t="n">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>91</v>
       </c>
       <c r="E181" t="n">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="F181" t="n">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="182">
@@ -6250,16 +6250,16 @@
         <v>74</v>
       </c>
       <c r="E182" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F182" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183">
@@ -6314,13 +6314,13 @@
         <v>45</v>
       </c>
       <c r="E184" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F184" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G184" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>27</v>
       </c>
       <c r="E185" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F185" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -6378,13 +6378,13 @@
         <v>27</v>
       </c>
       <c r="E186" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F186" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G186" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -6410,13 +6410,13 @@
         <v>26</v>
       </c>
       <c r="E187" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F187" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G187" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -7082,16 +7082,16 @@
         <v>6</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G208" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="209">
@@ -7114,16 +7114,16 @@
         <v>12</v>
       </c>
       <c r="E209" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="F209" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="210">
@@ -7146,13 +7146,13 @@
         <v>367</v>
       </c>
       <c r="E210" t="n">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="F210" t="n">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="G210" t="n">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -7178,13 +7178,13 @@
         <v>385</v>
       </c>
       <c r="E211" t="n">
-        <v>286</v>
+        <v>161</v>
       </c>
       <c r="F211" t="n">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="G211" t="n">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -7210,13 +7210,13 @@
         <v>402</v>
       </c>
       <c r="E212" t="n">
-        <v>376</v>
+        <v>256</v>
       </c>
       <c r="F212" t="n">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="G212" t="n">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -7242,13 +7242,13 @@
         <v>422</v>
       </c>
       <c r="E213" t="n">
-        <v>406</v>
+        <v>306</v>
       </c>
       <c r="F213" t="n">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="G213" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7274,13 +7274,13 @@
         <v>438</v>
       </c>
       <c r="E214" t="n">
-        <v>406</v>
+        <v>368</v>
       </c>
       <c r="F214" t="n">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="G214" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -7306,13 +7306,13 @@
         <v>438</v>
       </c>
       <c r="E215" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F215" t="n">
-        <v>238</v>
+        <v>413</v>
       </c>
       <c r="G215" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>440</v>
       </c>
       <c r="E216" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F216" t="n">
-        <v>238</v>
+        <v>413</v>
       </c>
       <c r="G216" t="n">
-        <v>202</v>
+        <v>27</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7370,13 +7370,13 @@
         <v>472</v>
       </c>
       <c r="E217" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F217" t="n">
-        <v>250</v>
+        <v>403</v>
       </c>
       <c r="G217" t="n">
-        <v>222</v>
+        <v>69</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -7402,13 +7402,13 @@
         <v>472</v>
       </c>
       <c r="E218" t="n">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="F218" t="n">
-        <v>195</v>
+        <v>388</v>
       </c>
       <c r="G218" t="n">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -7434,13 +7434,13 @@
         <v>472</v>
       </c>
       <c r="E219" t="n">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="F219" t="n">
-        <v>237</v>
+        <v>418</v>
       </c>
       <c r="G219" t="n">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7469,10 +7469,10 @@
         <v>418</v>
       </c>
       <c r="F220" t="n">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="G220" t="n">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7501,10 +7501,10 @@
         <v>418</v>
       </c>
       <c r="F221" t="n">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="G221" t="n">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -7533,10 +7533,10 @@
         <v>418</v>
       </c>
       <c r="F222" t="n">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="G222" t="n">
-        <v>222</v>
+        <v>54</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         <v>418</v>
       </c>
       <c r="F223" t="n">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="G223" t="n">
-        <v>221</v>
+        <v>53</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -7597,10 +7597,10 @@
         <v>418</v>
       </c>
       <c r="F224" t="n">
-        <v>250</v>
+        <v>418</v>
       </c>
       <c r="G224" t="n">
-        <v>218</v>
+        <v>50</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7626,13 +7626,13 @@
         <v>462</v>
       </c>
       <c r="E225" t="n">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="F225" t="n">
-        <v>250</v>
+        <v>403</v>
       </c>
       <c r="G225" t="n">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -7658,13 +7658,13 @@
         <v>438</v>
       </c>
       <c r="E226" t="n">
-        <v>418</v>
+        <v>343</v>
       </c>
       <c r="F226" t="n">
-        <v>250</v>
+        <v>343</v>
       </c>
       <c r="G226" t="n">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -7690,13 +7690,13 @@
         <v>431</v>
       </c>
       <c r="E227" t="n">
-        <v>388</v>
+        <v>272</v>
       </c>
       <c r="F227" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="G227" t="n">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -7722,13 +7722,13 @@
         <v>216</v>
       </c>
       <c r="E228" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F228" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="G228" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>105</v>
       </c>
       <c r="E229" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="F229" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="230">
@@ -7786,16 +7786,16 @@
         <v>87</v>
       </c>
       <c r="E230" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F230" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
@@ -7818,13 +7818,13 @@
         <v>73</v>
       </c>
       <c r="E231" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F231" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G231" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7850,13 +7850,13 @@
         <v>52</v>
       </c>
       <c r="E232" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="F232" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G232" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7882,13 +7882,13 @@
         <v>35</v>
       </c>
       <c r="E233" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F233" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G233" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>35</v>
       </c>
       <c r="E234" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F234" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G234" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7946,13 +7946,13 @@
         <v>34</v>
       </c>
       <c r="E235" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F235" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G235" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -8685,10 +8685,10 @@
         <v>204</v>
       </c>
       <c r="F258" t="n">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="G258" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -8717,10 +8717,10 @@
         <v>204</v>
       </c>
       <c r="F259" t="n">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="G259" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -8749,10 +8749,10 @@
         <v>206</v>
       </c>
       <c r="F260" t="n">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="G260" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -8781,10 +8781,10 @@
         <v>207</v>
       </c>
       <c r="F261" t="n">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="G261" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -8813,10 +8813,10 @@
         <v>208</v>
       </c>
       <c r="F262" t="n">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="G262" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8845,10 +8845,10 @@
         <v>208</v>
       </c>
       <c r="F263" t="n">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="G263" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8877,10 +8877,10 @@
         <v>209</v>
       </c>
       <c r="F264" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="G264" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8909,10 +8909,10 @@
         <v>209</v>
       </c>
       <c r="F265" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="G265" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8938,13 +8938,13 @@
         <v>209</v>
       </c>
       <c r="E266" t="n">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F266" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="G266" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8973,10 +8973,10 @@
         <v>209</v>
       </c>
       <c r="F267" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="G267" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -9005,10 +9005,10 @@
         <v>209</v>
       </c>
       <c r="F268" t="n">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="G268" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -9037,10 +9037,10 @@
         <v>208</v>
       </c>
       <c r="F269" t="n">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="G269" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -9069,10 +9069,10 @@
         <v>205</v>
       </c>
       <c r="F270" t="n">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="G270" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -9098,13 +9098,13 @@
         <v>205</v>
       </c>
       <c r="E271" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F271" t="n">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="G271" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>201</v>
       </c>
       <c r="F272" t="n">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="G272" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -9165,10 +9165,10 @@
         <v>201</v>
       </c>
       <c r="F273" t="n">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="G273" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -9197,10 +9197,10 @@
         <v>198</v>
       </c>
       <c r="F274" t="n">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="G274" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -9226,13 +9226,13 @@
         <v>198</v>
       </c>
       <c r="E275" t="n">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F275" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="G275" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -10221,10 +10221,10 @@
         <v>41</v>
       </c>
       <c r="F306" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G306" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -10253,10 +10253,10 @@
         <v>41</v>
       </c>
       <c r="F307" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G307" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -10285,10 +10285,10 @@
         <v>41</v>
       </c>
       <c r="F308" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G308" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -10317,10 +10317,10 @@
         <v>41</v>
       </c>
       <c r="F309" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G309" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -10349,10 +10349,10 @@
         <v>42</v>
       </c>
       <c r="F310" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G310" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -10381,10 +10381,10 @@
         <v>42</v>
       </c>
       <c r="F311" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G311" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -10413,10 +10413,10 @@
         <v>42</v>
       </c>
       <c r="F312" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G312" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -10445,10 +10445,10 @@
         <v>42</v>
       </c>
       <c r="F313" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G313" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -10477,10 +10477,10 @@
         <v>42</v>
       </c>
       <c r="F314" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G314" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -10509,10 +10509,10 @@
         <v>42</v>
       </c>
       <c r="F315" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G315" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -10541,10 +10541,10 @@
         <v>42</v>
       </c>
       <c r="F316" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G316" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -10573,10 +10573,10 @@
         <v>42</v>
       </c>
       <c r="F317" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G317" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -10605,10 +10605,10 @@
         <v>42</v>
       </c>
       <c r="F318" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G318" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -10637,10 +10637,10 @@
         <v>42</v>
       </c>
       <c r="F319" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G319" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -10669,10 +10669,10 @@
         <v>42</v>
       </c>
       <c r="F320" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G320" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -10701,10 +10701,10 @@
         <v>42</v>
       </c>
       <c r="F321" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G321" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -10733,10 +10733,10 @@
         <v>42</v>
       </c>
       <c r="F322" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G322" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -10765,10 +10765,10 @@
         <v>42</v>
       </c>
       <c r="F323" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G323" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
